--- a/artfynd/A 14102-2025 artfynd.xlsx
+++ b/artfynd/A 14102-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>71286174</v>
+        <v>71286136</v>
       </c>
       <c r="B2" t="n">
-        <v>55853</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100103</v>
+        <v>100045</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brushane</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calidris pugnax</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>98</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>414130.5257080046</v>
+        <v>414131</v>
       </c>
       <c r="R2" t="n">
-        <v>6437740.590348095</v>
+        <v>6437741</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -774,6 +769,11 @@
           <t>12:10</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Översvärmat gärde</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -795,6 +795,246 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>71286164</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57258</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ruvande</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skattegården Vårkumla, Vårkumla, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>414131</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6437741</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vårkumla</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2018-05-13</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2018-05-13</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Ingvor Ljuhs</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ingvor Ljuhs</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>71286174</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57397</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100103</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Brushane</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Calidris pugnax</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skattegården Vårkumla, Vårkumla, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>414131</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6437741</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vårkumla</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-05-13</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-05-13</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ingvor Ljuhs</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ingvor Ljuhs</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
